--- a/docs/downloads/08/tbl_produits_elevage_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_marovoay_madiromiongana.xlsx
@@ -412,9 +412,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -442,9 +439,6 @@
           <t>Trondro Nompian</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -457,9 +451,6 @@
           <t>Vorona</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -547,9 +538,6 @@
           <t>Trondro Nompian</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -561,9 +549,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C14">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
